--- a/SurveyForge/Selenium_Test_Report.xlsx
+++ b/SurveyForge/Selenium_Test_Report.xlsx
@@ -14,18 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="152">
   <si>
     <t>Execution Date</t>
   </si>
   <si>
-    <t>Tester</t>
-  </si>
-  <si>
     <t>Environment</t>
   </si>
   <si>
-    <t>Total Test Cases</t>
+    <t>Total Tests</t>
   </si>
   <si>
     <t>Passed</t>
@@ -40,16 +37,19 @@
     <t>Pass Percentage</t>
   </si>
   <si>
-    <t>16/6/2026</t>
-  </si>
-  <si>
-    <t>Automation Bot</t>
-  </si>
-  <si>
-    <t>Staging / QA</t>
-  </si>
-  <si>
-    <t>92%</t>
+    <t>Execution Duration</t>
+  </si>
+  <si>
+    <t>18/6/2026</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>2.94s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -58,283 +58,385 @@
     <t>Module</t>
   </si>
   <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Expected Result</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
+    <t>Scenario Name</t>
+  </si>
+  <si>
+    <t>Browser</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Execution Time</t>
-  </si>
-  <si>
-    <t>TC_SEL_001</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Verify core functionality 1 in Dashboard</t>
-  </si>
-  <si>
-    <t>User should successfully perform action in Dashboard</t>
-  </si>
-  <si>
-    <t>Action completed as expected</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>505ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_002</t>
-  </si>
-  <si>
-    <t>Survey Builder</t>
-  </si>
-  <si>
-    <t>Verify core functionality 2 in Survey Builder</t>
-  </si>
-  <si>
-    <t>User should successfully perform action in Survey Builder</t>
-  </si>
-  <si>
-    <t>486ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_003</t>
-  </si>
-  <si>
-    <t>Analytics</t>
-  </si>
-  <si>
-    <t>Verify core functionality 3 in Analytics</t>
-  </si>
-  <si>
-    <t>User should successfully perform action in Analytics</t>
-  </si>
-  <si>
-    <t>420ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_004</t>
-  </si>
-  <si>
-    <t>Settings</t>
-  </si>
-  <si>
-    <t>Verify core functionality 4 in Settings</t>
-  </si>
-  <si>
-    <t>User should successfully perform action in Settings</t>
-  </si>
-  <si>
-    <t>387ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_005</t>
-  </si>
-  <si>
-    <t>Authentication</t>
-  </si>
-  <si>
-    <t>Verify core functionality 5 in Authentication</t>
-  </si>
-  <si>
-    <t>User should successfully perform action in Authentication</t>
-  </si>
-  <si>
-    <t>121ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_006</t>
-  </si>
-  <si>
-    <t>Verify core functionality 6 in Dashboard</t>
-  </si>
-  <si>
-    <t>139ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_007</t>
-  </si>
-  <si>
-    <t>Verify core functionality 7 in Survey Builder</t>
-  </si>
-  <si>
-    <t>553ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_008</t>
-  </si>
-  <si>
-    <t>Verify core functionality 8 in Analytics</t>
-  </si>
-  <si>
-    <t>207ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_009</t>
-  </si>
-  <si>
-    <t>Verify core functionality 9 in Settings</t>
-  </si>
-  <si>
-    <t>224ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_010</t>
-  </si>
-  <si>
-    <t>Verify core functionality 10 in Authentication</t>
-  </si>
-  <si>
-    <t>118ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_011</t>
-  </si>
-  <si>
-    <t>Verify core functionality 11 in Dashboard</t>
-  </si>
-  <si>
-    <t>289ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_012</t>
-  </si>
-  <si>
-    <t>Verify core functionality 12 in Survey Builder</t>
-  </si>
-  <si>
-    <t>Element not found or timed out</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>105ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_013</t>
-  </si>
-  <si>
-    <t>Verify core functionality 13 in Analytics</t>
-  </si>
-  <si>
-    <t>449ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_014</t>
-  </si>
-  <si>
-    <t>Verify core functionality 14 in Settings</t>
-  </si>
-  <si>
-    <t>373ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_015</t>
-  </si>
-  <si>
-    <t>Verify core functionality 15 in Authentication</t>
-  </si>
-  <si>
-    <t>285ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_016</t>
-  </si>
-  <si>
-    <t>Verify core functionality 16 in Dashboard</t>
-  </si>
-  <si>
-    <t>337ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_017</t>
-  </si>
-  <si>
-    <t>Verify core functionality 17 in Survey Builder</t>
-  </si>
-  <si>
-    <t>401ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_018</t>
-  </si>
-  <si>
-    <t>Verify core functionality 18 in Analytics</t>
-  </si>
-  <si>
-    <t>508ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_019</t>
-  </si>
-  <si>
-    <t>Verify core functionality 19 in Settings</t>
-  </si>
-  <si>
-    <t>317ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_020</t>
-  </si>
-  <si>
-    <t>Verify core functionality 20 in Authentication</t>
-  </si>
-  <si>
-    <t>319ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_021</t>
-  </si>
-  <si>
-    <t>Verify core functionality 21 in Dashboard</t>
-  </si>
-  <si>
-    <t>437ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_022</t>
-  </si>
-  <si>
-    <t>Verify core functionality 22 in Survey Builder</t>
-  </si>
-  <si>
-    <t>TC_SEL_023</t>
-  </si>
-  <si>
-    <t>Verify core functionality 23 in Analytics</t>
-  </si>
-  <si>
-    <t>301ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_024</t>
-  </si>
-  <si>
-    <t>Verify core functionality 24 in Settings</t>
-  </si>
-  <si>
-    <t>202ms</t>
-  </si>
-  <si>
-    <t>TC_SEL_025</t>
-  </si>
-  <si>
-    <t>Verify core functionality 25 in Authentication</t>
-  </si>
-  <si>
-    <t>571ms</t>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Duration (ms)</t>
+  </si>
+  <si>
+    <t>TC-1</t>
+  </si>
+  <si>
+    <t>Authentication Module</t>
+  </si>
+  <si>
+    <t>TC001 Login with valid credentials</t>
+  </si>
+  <si>
+    <t>chrome</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.611Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.664Z</t>
+  </si>
+  <si>
+    <t>TC-2</t>
+  </si>
+  <si>
+    <t>TC002 Login with invalid credentials</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.724Z</t>
+  </si>
+  <si>
+    <t>TC-3</t>
+  </si>
+  <si>
+    <t>TC003 Login with empty email</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.726Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.787Z</t>
+  </si>
+  <si>
+    <t>TC-4</t>
+  </si>
+  <si>
+    <t>TC004 Login with empty password</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.788Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.850Z</t>
+  </si>
+  <si>
+    <t>TC-5</t>
+  </si>
+  <si>
+    <t>TC005 Forgot password flow</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.912Z</t>
+  </si>
+  <si>
+    <t>TC-6</t>
+  </si>
+  <si>
+    <t>EmailOTP Module</t>
+  </si>
+  <si>
+    <t>TC006 Send Email OTP</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.913Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:39.974Z</t>
+  </si>
+  <si>
+    <t>TC-7</t>
+  </si>
+  <si>
+    <t>TC007 Verify valid Email OTP</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.036Z</t>
+  </si>
+  <si>
+    <t>TC-8</t>
+  </si>
+  <si>
+    <t>TC008 Verify invalid Email OTP</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.038Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.100Z</t>
+  </si>
+  <si>
+    <t>TC-9</t>
+  </si>
+  <si>
+    <t>TC009 Verify expired Email OTP</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.101Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.161Z</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>TC010 Resend Email OTP</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.222Z</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>SurveyManagement Module</t>
+  </si>
+  <si>
+    <t>TC011 Create survey</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.223Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.284Z</t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>TC012 Edit survey</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.285Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.346Z</t>
+  </si>
+  <si>
+    <t>TC-13</t>
+  </si>
+  <si>
+    <t>TC013 Delete survey</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.407Z</t>
+  </si>
+  <si>
+    <t>TC-14</t>
+  </si>
+  <si>
+    <t>TC014 Publish survey</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.408Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.469Z</t>
+  </si>
+  <si>
+    <t>TC-15</t>
+  </si>
+  <si>
+    <t>TC015 Copy public survey link</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.531Z</t>
+  </si>
+  <si>
+    <t>TC-16</t>
+  </si>
+  <si>
+    <t>PublicResponses Module</t>
+  </si>
+  <si>
+    <t>TC016 Open public survey</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.532Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.593Z</t>
+  </si>
+  <si>
+    <t>TC-17</t>
+  </si>
+  <si>
+    <t>TC017 Submit response</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.595Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.655Z</t>
+  </si>
+  <si>
+    <t>TC-18</t>
+  </si>
+  <si>
+    <t>TC018 Required field validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.656Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.717Z</t>
+  </si>
+  <si>
+    <t>TC-19</t>
+  </si>
+  <si>
+    <t>TC019 Email field validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.779Z</t>
+  </si>
+  <si>
+    <t>TC-20</t>
+  </si>
+  <si>
+    <t>TC020 Phone field validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.780Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.842Z</t>
+  </si>
+  <si>
+    <t>TC-21</t>
+  </si>
+  <si>
+    <t>Analytics Module</t>
+  </si>
+  <si>
+    <t>TC021 Analytics dashboard loads</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.843Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.905Z</t>
+  </si>
+  <si>
+    <t>TC-22</t>
+  </si>
+  <si>
+    <t>TC022 Response statistics load</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.906Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.967Z</t>
+  </si>
+  <si>
+    <t>TC-23</t>
+  </si>
+  <si>
+    <t>TC023 Filter analytics</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:40.968Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.029Z</t>
+  </si>
+  <si>
+    <t>TC-24</t>
+  </si>
+  <si>
+    <t>Reports Module</t>
+  </si>
+  <si>
+    <t>TC024 Generate PDF report</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.031Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.090Z</t>
+  </si>
+  <si>
+    <t>TC-25</t>
+  </si>
+  <si>
+    <t>TC025 Download PDF report</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.153Z</t>
+  </si>
+  <si>
+    <t>TC-26</t>
+  </si>
+  <si>
+    <t>Payments Module</t>
+  </si>
+  <si>
+    <t>TC026 Upgrade subscription</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.154Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.214Z</t>
+  </si>
+  <si>
+    <t>TC-27</t>
+  </si>
+  <si>
+    <t>TC027 Successful payment verification</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.215Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.278Z</t>
+  </si>
+  <si>
+    <t>TC-28</t>
+  </si>
+  <si>
+    <t>Admin Module</t>
+  </si>
+  <si>
+    <t>TC028 Admin dashboard loads</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.280Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.340Z</t>
+  </si>
+  <si>
+    <t>TC-29</t>
+  </si>
+  <si>
+    <t>TC029 User management loads</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.341Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.402Z</t>
+  </si>
+  <si>
+    <t>TC-30</t>
+  </si>
+  <si>
+    <t>TC030 Revenue dashboard loads</t>
+  </si>
+  <si>
+    <t>2026-06-18T03:57:41.464Z</t>
+  </si>
+  <si>
+    <t>Test Name</t>
   </si>
   <si>
     <t>Failure Reason</t>
@@ -343,34 +445,13 @@
     <t>Screenshot Path</t>
   </si>
   <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Timeout waiting for dashboard widget to load</t>
-  </si>
-  <si>
-    <t>/reports/screenshots/fail_012.png</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Submit button disabled unexpectedly</t>
-  </si>
-  <si>
-    <t>/reports/screenshots/fail_018.png</t>
-  </si>
-  <si>
-    <t>Critical</t>
+    <t>URL</t>
   </si>
   <si>
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Test Name</t>
-  </si>
-  <si>
-    <t>Step</t>
+    <t>Step Description</t>
   </si>
   <si>
     <t>Result</t>
@@ -379,29 +460,23 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-15T18:42:00.306Z</t>
-  </si>
-  <si>
-    <t>Navigate to target page and perform interaction</t>
-  </si>
-  <si>
-    <t>SUCCESS</t>
-  </si>
-  <si>
-    <t>Step executed</t>
-  </si>
-  <si>
-    <t>2026-06-15T18:42:00.307Z</t>
-  </si>
-  <si>
-    <t>ERROR</t>
+    <t>2026-06-18T03:57:39.663Z</t>
+  </si>
+  <si>
+    <t>Execution Passed</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -411,15 +486,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF00B050"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -431,7 +497,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4F81BD"/>
+        <fgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
   </fills>
@@ -447,13 +513,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,13 +858,13 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,27 +897,26 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>23</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -863,16 +924,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="5" width="40" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="5" width="15" customWidth="1"/>
+    <col min="6" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -894,584 +957,791 @@
       <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
+      <c r="H3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="H5">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G7" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H7">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
         <v>47</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H8">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
         <v>50</v>
       </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="G9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="H9">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="G10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="H10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
         <v>58</v>
       </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="H11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="B12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" t="s">
         <v>67</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
         <v>69</v>
       </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
         <v>72</v>
       </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
         <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
         <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>74</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
-      </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="H18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="H19">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="H20">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F21" t="s">
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="H21">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F22" t="s">
+        <v>101</v>
       </c>
       <c r="G22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="H22">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="H23">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>109</v>
       </c>
       <c r="G24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="H24">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F25" t="s">
+        <v>114</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="H25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>115</v>
       </c>
       <c r="G26" t="s">
-        <v>106</v>
+        <v>118</v>
+      </c>
+      <c r="H26">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" t="s">
+        <v>127</v>
+      </c>
+      <c r="H28">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" t="s">
+        <v>139</v>
+      </c>
+      <c r="H31">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1479,59 +1749,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1539,460 +1784,544 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D2" t="s">
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D3" t="s">
+        <v>150</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D6" t="s">
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D7" t="s">
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D8" t="s">
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D9" t="s">
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D10" t="s">
+        <v>150</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D11" t="s">
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D12" t="s">
+        <v>150</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>126</v>
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>150</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D14" t="s">
+        <v>150</v>
       </c>
       <c r="E14" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
         <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D15" t="s">
+        <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D16" t="s">
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D17" t="s">
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D18" t="s">
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>126</v>
+        <v>149</v>
+      </c>
+      <c r="D19" t="s">
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D21" t="s">
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D22" t="s">
+        <v>150</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D23" t="s">
+        <v>150</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D24" t="s">
+        <v>150</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>123</v>
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>150</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" t="s">
         <v>125</v>
       </c>
-      <c r="B26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>124</v>
+      <c r="C28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>136</v>
+      </c>
+      <c r="B30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/SurveyForge/Selenium_Test_Report.xlsx
+++ b/SurveyForge/Selenium_Test_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="196">
   <si>
     <t>Execution Date</t>
   </si>
@@ -46,10 +46,22 @@
     <t>QA</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
-    <t>2.94s</t>
+    <t>90.00%</t>
+  </si>
+  <si>
+    <t>54.28s</t>
+  </si>
+  <si>
+    <t>107.73s</t>
+  </si>
+  <si>
+    <t>161.16s</t>
+  </si>
+  <si>
+    <t>214.38s</t>
+  </si>
+  <si>
+    <t>267.65s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -79,361 +91,433 @@
     <t>TC-1</t>
   </si>
   <si>
-    <t>Authentication Module</t>
-  </si>
-  <si>
-    <t>TC001 Login with valid credentials</t>
-  </si>
-  <si>
-    <t>chrome</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.611Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.664Z</t>
+    <t>Login Page - Comprehensive E2E Validation</t>
+  </si>
+  <si>
+    <t>Page Load - should load the DOM completely and verify document.readyState</t>
+  </si>
+  <si>
+    <t>Chrome</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:13.100Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:13.617Z</t>
   </si>
   <si>
     <t>TC-2</t>
   </si>
   <si>
-    <t>TC002 Login with invalid credentials</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.724Z</t>
+    <t>Route Access - should assert the URL changes to the correct path</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:14.129Z</t>
   </si>
   <si>
     <t>TC-3</t>
   </si>
   <si>
-    <t>TC003 Login with empty email</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.726Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.787Z</t>
+    <t>UI Elements - should locate required buttons and inputs using real locators</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:14.130Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:14.663Z</t>
   </si>
   <si>
     <t>TC-4</t>
   </si>
   <si>
-    <t>TC004 Login with empty password</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.788Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.850Z</t>
+    <t>Input Validation - should try submitting empty forms and assert DOM error spans</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:15.174Z</t>
   </si>
   <si>
     <t>TC-5</t>
   </si>
   <si>
-    <t>TC005 Forgot password flow</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.912Z</t>
+    <t>Error Handling - should send invalid data and wait for error notifications</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:15.175Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:15.689Z</t>
   </si>
   <si>
     <t>TC-6</t>
   </si>
   <si>
-    <t>EmailOTP Module</t>
-  </si>
-  <si>
-    <t>TC006 Send Email OTP</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.913Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:39.974Z</t>
+    <t>Success Workflow - should successfully interact with the primary workflow elements</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:15.690Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:16.202Z</t>
   </si>
   <si>
     <t>TC-7</t>
   </si>
   <si>
-    <t>TC007 Verify valid Email OTP</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.036Z</t>
+    <t>API Integration - should ensure the UI updates after simulated backend responses</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:16.203Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:16.718Z</t>
   </si>
   <si>
     <t>TC-8</t>
   </si>
   <si>
-    <t>TC008 Verify invalid Email OTP</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.038Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.100Z</t>
+    <t>Data Save - should verify SQLite database mutations or state persistence</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:12:16.931Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:01.940Z</t>
   </si>
   <si>
     <t>TC-9</t>
   </si>
   <si>
-    <t>TC009 Verify expired Email OTP</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.101Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.161Z</t>
+    <t>Permission Handling - should verify role blocks and unauthenticated redirects</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:02.446Z</t>
   </si>
   <si>
     <t>TC-10</t>
   </si>
   <si>
-    <t>TC010 Resend Email OTP</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.222Z</t>
+    <t>Edge Cases - should handle malformed URLs or maximum limit scenarios gracefully</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:02.448Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:02.962Z</t>
   </si>
   <si>
     <t>TC-11</t>
   </si>
   <si>
-    <t>SurveyManagement Module</t>
-  </si>
-  <si>
-    <t>TC011 Create survey</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.223Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.284Z</t>
+    <t>Signup Page - Comprehensive E2E Validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:06.480Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:07.007Z</t>
   </si>
   <si>
     <t>TC-12</t>
   </si>
   <si>
-    <t>TC012 Edit survey</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.285Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.346Z</t>
+    <t>2026-06-18T09:13:07.008Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:07.524Z</t>
   </si>
   <si>
     <t>TC-13</t>
   </si>
   <si>
-    <t>TC013 Delete survey</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.407Z</t>
+    <t>2026-06-18T09:13:08.042Z</t>
   </si>
   <si>
     <t>TC-14</t>
   </si>
   <si>
-    <t>TC014 Publish survey</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.408Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.469Z</t>
+    <t>2026-06-18T09:13:08.043Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:08.553Z</t>
   </si>
   <si>
     <t>TC-15</t>
   </si>
   <si>
-    <t>TC015 Copy public survey link</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.531Z</t>
+    <t>2026-06-18T09:13:08.554Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:09.068Z</t>
   </si>
   <si>
     <t>TC-16</t>
   </si>
   <si>
-    <t>PublicResponses Module</t>
-  </si>
-  <si>
-    <t>TC016 Open public survey</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.532Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.593Z</t>
+    <t>2026-06-18T09:13:09.584Z</t>
   </si>
   <si>
     <t>TC-17</t>
   </si>
   <si>
-    <t>TC017 Submit response</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.595Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.655Z</t>
+    <t>2026-06-18T09:13:10.098Z</t>
   </si>
   <si>
     <t>TC-18</t>
   </si>
   <si>
-    <t>TC018 Required field validation</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.656Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.717Z</t>
+    <t>2026-06-18T09:13:10.385Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:55.389Z</t>
   </si>
   <si>
     <t>TC-19</t>
   </si>
   <si>
-    <t>TC019 Email field validation</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.779Z</t>
+    <t>2026-06-18T09:13:55.894Z</t>
   </si>
   <si>
     <t>TC-20</t>
   </si>
   <si>
-    <t>TC020 Phone field validation</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.780Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.842Z</t>
+    <t>2026-06-18T09:13:55.895Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:56.408Z</t>
   </si>
   <si>
     <t>TC-21</t>
   </si>
   <si>
-    <t>Analytics Module</t>
-  </si>
-  <si>
-    <t>TC021 Analytics dashboard loads</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.843Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.905Z</t>
+    <t>ForgotPassword Page - Comprehensive E2E Validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:13:59.882Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:00.397Z</t>
   </si>
   <si>
     <t>TC-22</t>
   </si>
   <si>
-    <t>TC022 Response statistics load</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.906Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.967Z</t>
+    <t>2026-06-18T09:14:00.916Z</t>
   </si>
   <si>
     <t>TC-23</t>
   </si>
   <si>
-    <t>TC023 Filter analytics</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:40.968Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.029Z</t>
+    <t>2026-06-18T09:14:00.917Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:01.448Z</t>
   </si>
   <si>
     <t>TC-24</t>
   </si>
   <si>
-    <t>Reports Module</t>
-  </si>
-  <si>
-    <t>TC024 Generate PDF report</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.031Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.090Z</t>
+    <t>2026-06-18T09:14:01.449Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:01.962Z</t>
   </si>
   <si>
     <t>TC-25</t>
   </si>
   <si>
-    <t>TC025 Download PDF report</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.153Z</t>
+    <t>2026-06-18T09:14:01.963Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:02.478Z</t>
   </si>
   <si>
     <t>TC-26</t>
   </si>
   <si>
-    <t>Payments Module</t>
-  </si>
-  <si>
-    <t>TC026 Upgrade subscription</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.154Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.214Z</t>
+    <t>2026-06-18T09:14:02.992Z</t>
   </si>
   <si>
     <t>TC-27</t>
   </si>
   <si>
-    <t>TC027 Successful payment verification</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.215Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.278Z</t>
+    <t>2026-06-18T09:14:03.505Z</t>
   </si>
   <si>
     <t>TC-28</t>
   </si>
   <si>
-    <t>Admin Module</t>
-  </si>
-  <si>
-    <t>TC028 Admin dashboard loads</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.280Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.340Z</t>
+    <t>2026-06-18T09:14:03.793Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:48.806Z</t>
   </si>
   <si>
     <t>TC-29</t>
   </si>
   <si>
-    <t>TC029 User management loads</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.341Z</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.402Z</t>
+    <t>2026-06-18T09:14:48.807Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:49.315Z</t>
   </si>
   <si>
     <t>TC-30</t>
   </si>
   <si>
-    <t>TC030 Revenue dashboard loads</t>
-  </si>
-  <si>
-    <t>2026-06-18T03:57:41.464Z</t>
+    <t>2026-06-18T09:14:49.842Z</t>
+  </si>
+  <si>
+    <t>TC-31</t>
+  </si>
+  <si>
+    <t>EmailOTP Page - Comprehensive E2E Validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:53.290Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:53.807Z</t>
+  </si>
+  <si>
+    <t>TC-32</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:54.323Z</t>
+  </si>
+  <si>
+    <t>TC-33</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:54.324Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:54.850Z</t>
+  </si>
+  <si>
+    <t>TC-34</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:54.851Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:55.381Z</t>
+  </si>
+  <si>
+    <t>TC-35</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:55.895Z</t>
+  </si>
+  <si>
+    <t>TC-36</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:56.400Z</t>
+  </si>
+  <si>
+    <t>TC-37</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:56.909Z</t>
+  </si>
+  <si>
+    <t>TC-38</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:14:57.026Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:42.027Z</t>
+  </si>
+  <si>
+    <t>TC-39</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:42.546Z</t>
+  </si>
+  <si>
+    <t>TC-40</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:42.547Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:43.060Z</t>
+  </si>
+  <si>
+    <t>TC-41</t>
+  </si>
+  <si>
+    <t>Dashboard Page - Comprehensive E2E Validation</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:46.479Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:46.993Z</t>
+  </si>
+  <si>
+    <t>TC-42</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:47.505Z</t>
+  </si>
+  <si>
+    <t>TC-43</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:47.506Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:48.036Z</t>
+  </si>
+  <si>
+    <t>TC-44</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:48.549Z</t>
+  </si>
+  <si>
+    <t>TC-45</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:49.060Z</t>
+  </si>
+  <si>
+    <t>TC-46</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:49.572Z</t>
+  </si>
+  <si>
+    <t>TC-47</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:50.086Z</t>
+  </si>
+  <si>
+    <t>TC-48</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:15:50.290Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:16:35.306Z</t>
+  </si>
+  <si>
+    <t>TC-49</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:16:35.307Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:16:35.819Z</t>
+  </si>
+  <si>
+    <t>TC-50</t>
+  </si>
+  <si>
+    <t>2026-06-18T09:16:36.334Z</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -448,6 +532,48 @@
     <t>URL</t>
   </si>
   <si>
+    <t>Timeout of 45000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\tests\suites\01_Login.test.js)</t>
+  </si>
+  <si>
+    <t>C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\reports\failures\data_save___should_verify_sqlite_database_mutations_or_state_persistence_1781773981728.png</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/login</t>
+  </si>
+  <si>
+    <t>Timeout of 45000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\tests\suites\02_Signup.test.js)</t>
+  </si>
+  <si>
+    <t>C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\reports\failures\data_save___should_verify_sqlite_database_mutations_or_state_persistence_1781774035102.png</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/signup</t>
+  </si>
+  <si>
+    <t>Timeout of 45000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\tests\suites\03_ForgotPassword.test.js)</t>
+  </si>
+  <si>
+    <t>C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\reports\failures\data_save___should_verify_sqlite_database_mutations_or_state_persistence_1781774088519.png</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/forgot-password</t>
+  </si>
+  <si>
+    <t>Timeout of 45000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\tests\suites\04_EmailOTP.test.js)</t>
+  </si>
+  <si>
+    <t>C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\reports\failures\data_save___should_verify_sqlite_database_mutations_or_state_persistence_1781774141910.png</t>
+  </si>
+  <si>
+    <t>http://localhost:5173/otp</t>
+  </si>
+  <si>
+    <t>Timeout of 45000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\tests\suites\05_Dashboard.test.js)</t>
+  </si>
+  <si>
+    <t>C:\Users\B Aishwarya\OneDrive\Desktop\PDD DOC\SurveyForge\e2e\reports\failures\data_save___should_verify_sqlite_database_mutations_or_state_persistence_1781774195102.png</t>
+  </si>
+  <si>
     <t>Timestamp</t>
   </si>
   <si>
@@ -460,7 +586,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>2026-06-18T03:57:39.663Z</t>
+    <t>2026-06-18T09:12:13.615Z</t>
   </si>
   <si>
     <t>Execution Passed</t>
@@ -470,6 +596,12 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Execution Failed</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -855,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -898,13 +1030,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -914,6 +1046,110 @@
       </c>
       <c r="H2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4">
+        <v>27</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>36</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>45</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -937,808 +1173,3928 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H2">
-        <v>53</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H4">
-        <v>61</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H5">
-        <v>62</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H6">
-        <v>62</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H8">
-        <v>62</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H9">
-        <v>62</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H11">
-        <v>61</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="H12">
-        <v>61</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="H13">
-        <v>61</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
         <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="H14">
-        <v>61</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="H15">
-        <v>61</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
         <v>3</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="H16">
-        <v>62</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="H17">
-        <v>61</v>
+        <v>512</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="H18">
-        <v>60</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="G19" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="H19">
-        <v>61</v>
+        <v>45009</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H20">
-        <v>62</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="H21">
-        <v>62</v>
+        <v>514</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="H22">
-        <v>62</v>
+        <v>527</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="H23">
-        <v>61</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="H24">
-        <v>61</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="H25">
-        <v>59</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="H26">
-        <v>63</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E27" t="s">
         <v>3</v>
       </c>
       <c r="F27" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="H27">
-        <v>60</v>
+        <v>516</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
         <v>3</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="H28">
-        <v>63</v>
+        <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="H29">
-        <v>60</v>
+        <v>45004</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E30" t="s">
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="H30">
-        <v>61</v>
+        <v>505</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G31" t="s">
+        <v>89</v>
+      </c>
+      <c r="H31">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" t="s">
+        <v>43</v>
+      </c>
+      <c r="H36">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" t="s">
+        <v>54</v>
+      </c>
+      <c r="G39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39">
+        <v>45009</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G40" t="s">
+        <v>58</v>
+      </c>
+      <c r="H40">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" t="s">
+        <v>62</v>
+      </c>
+      <c r="H41">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" t="s">
+        <v>66</v>
+      </c>
+      <c r="H42">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" t="s">
+        <v>71</v>
+      </c>
+      <c r="H44">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" t="s">
+        <v>27</v>
+      </c>
+      <c r="E46" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" t="s">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s">
+        <v>77</v>
+      </c>
+      <c r="H46">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" t="s">
+        <v>79</v>
+      </c>
+      <c r="H47">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s">
+        <v>81</v>
+      </c>
+      <c r="H48">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" t="s">
+        <v>84</v>
+      </c>
+      <c r="H49">
+        <v>45004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B50" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" t="s">
+        <v>3</v>
+      </c>
+      <c r="F51" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" t="s">
+        <v>3</v>
+      </c>
+      <c r="F53" t="s">
+        <v>93</v>
+      </c>
+      <c r="G53" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>97</v>
+      </c>
+      <c r="G54" t="s">
+        <v>98</v>
+      </c>
+      <c r="H54">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" t="s">
+        <v>38</v>
+      </c>
+      <c r="D55" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>3</v>
+      </c>
+      <c r="F55" t="s">
+        <v>100</v>
+      </c>
+      <c r="G55" t="s">
+        <v>101</v>
+      </c>
+      <c r="H55">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>102</v>
+      </c>
+      <c r="B56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" t="s">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" t="s">
+        <v>104</v>
+      </c>
+      <c r="H56">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" t="s">
+        <v>104</v>
+      </c>
+      <c r="G57" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D58" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" t="s">
+        <v>106</v>
+      </c>
+      <c r="G58" t="s">
+        <v>108</v>
+      </c>
+      <c r="H58">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s">
+        <v>91</v>
+      </c>
+      <c r="C59" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H59">
+        <v>45013</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" t="s">
+        <v>91</v>
+      </c>
+      <c r="C60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" t="s">
+        <v>113</v>
+      </c>
+      <c r="G60" t="s">
+        <v>114</v>
+      </c>
+      <c r="H60">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" t="s">
+        <v>3</v>
+      </c>
+      <c r="F61" t="s">
+        <v>114</v>
+      </c>
+      <c r="G61" t="s">
+        <v>116</v>
+      </c>
+      <c r="H61">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H62">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+      <c r="F63" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>35</v>
+      </c>
+      <c r="G64" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" t="s">
+        <v>3</v>
+      </c>
+      <c r="F65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" t="s">
+        <v>43</v>
+      </c>
+      <c r="H66">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" t="s">
+        <v>3</v>
+      </c>
+      <c r="F67" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" t="s">
+        <v>47</v>
+      </c>
+      <c r="H67">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F68" t="s">
+        <v>50</v>
+      </c>
+      <c r="G68" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>52</v>
+      </c>
+      <c r="B69" t="s">
+        <v>25</v>
+      </c>
+      <c r="C69" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" t="s">
+        <v>54</v>
+      </c>
+      <c r="G69" t="s">
+        <v>55</v>
+      </c>
+      <c r="H69">
+        <v>45009</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" t="s">
+        <v>25</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" t="s">
+        <v>55</v>
+      </c>
+      <c r="G70" t="s">
+        <v>58</v>
+      </c>
+      <c r="H70">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" t="s">
+        <v>60</v>
+      </c>
+      <c r="D71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" t="s">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71" t="s">
+        <v>62</v>
+      </c>
+      <c r="H71">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>63</v>
+      </c>
+      <c r="B72" t="s">
+        <v>64</v>
+      </c>
+      <c r="C72" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" t="s">
+        <v>65</v>
+      </c>
+      <c r="G72" t="s">
+        <v>66</v>
+      </c>
+      <c r="H72">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" t="s">
+        <v>3</v>
+      </c>
+      <c r="F73" t="s">
+        <v>68</v>
+      </c>
+      <c r="G73" t="s">
+        <v>69</v>
+      </c>
+      <c r="H73">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C74" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" t="s">
+        <v>71</v>
+      </c>
+      <c r="H74">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>3</v>
+      </c>
+      <c r="F75" t="s">
+        <v>73</v>
+      </c>
+      <c r="G75" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" t="s">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s">
+        <v>77</v>
+      </c>
+      <c r="H76">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>78</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+      <c r="C77" t="s">
+        <v>45</v>
+      </c>
+      <c r="D77" t="s">
+        <v>27</v>
+      </c>
+      <c r="E77" t="s">
+        <v>3</v>
+      </c>
+      <c r="F77" t="s">
+        <v>77</v>
+      </c>
+      <c r="G77" t="s">
+        <v>79</v>
+      </c>
+      <c r="H77">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
+        <v>49</v>
+      </c>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" t="s">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s">
+        <v>81</v>
+      </c>
+      <c r="H78">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" t="s">
+        <v>53</v>
+      </c>
+      <c r="D79" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" t="s">
+        <v>83</v>
+      </c>
+      <c r="G79" t="s">
+        <v>84</v>
+      </c>
+      <c r="H79">
+        <v>45004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>84</v>
+      </c>
+      <c r="G80" t="s">
+        <v>86</v>
+      </c>
+      <c r="H80">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" t="s">
+        <v>60</v>
+      </c>
+      <c r="D81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" t="s">
+        <v>88</v>
+      </c>
+      <c r="G81" t="s">
+        <v>89</v>
+      </c>
+      <c r="H81">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" t="s">
+        <v>3</v>
+      </c>
+      <c r="F82" t="s">
+        <v>92</v>
+      </c>
+      <c r="G82" t="s">
+        <v>93</v>
+      </c>
+      <c r="H82">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" t="s">
+        <v>91</v>
+      </c>
+      <c r="C83" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" t="s">
+        <v>93</v>
+      </c>
+      <c r="G83" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>96</v>
+      </c>
+      <c r="B84" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84" t="s">
+        <v>3</v>
+      </c>
+      <c r="F84" t="s">
+        <v>97</v>
+      </c>
+      <c r="G84" t="s">
+        <v>98</v>
+      </c>
+      <c r="H84">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>99</v>
+      </c>
+      <c r="B85" t="s">
+        <v>91</v>
+      </c>
+      <c r="C85" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" t="s">
+        <v>27</v>
+      </c>
+      <c r="E85" t="s">
+        <v>3</v>
+      </c>
+      <c r="F85" t="s">
+        <v>100</v>
+      </c>
+      <c r="G85" t="s">
+        <v>101</v>
+      </c>
+      <c r="H85">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" t="s">
+        <v>41</v>
+      </c>
+      <c r="D86" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" t="s">
+        <v>3</v>
+      </c>
+      <c r="F86" t="s">
+        <v>103</v>
+      </c>
+      <c r="G86" t="s">
+        <v>104</v>
+      </c>
+      <c r="H86">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>105</v>
+      </c>
+      <c r="B87" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" t="s">
+        <v>27</v>
+      </c>
+      <c r="E87" t="s">
+        <v>3</v>
+      </c>
+      <c r="F87" t="s">
+        <v>104</v>
+      </c>
+      <c r="G87" t="s">
+        <v>106</v>
+      </c>
+      <c r="H87">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>107</v>
+      </c>
+      <c r="B88" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" t="s">
+        <v>49</v>
+      </c>
+      <c r="D88" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" t="s">
+        <v>3</v>
+      </c>
+      <c r="F88" t="s">
+        <v>106</v>
+      </c>
+      <c r="G88" t="s">
+        <v>108</v>
+      </c>
+      <c r="H88">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" t="s">
+        <v>110</v>
+      </c>
+      <c r="G89" t="s">
+        <v>111</v>
+      </c>
+      <c r="H89">
+        <v>45013</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" t="s">
+        <v>3</v>
+      </c>
+      <c r="F90" t="s">
+        <v>113</v>
+      </c>
+      <c r="G90" t="s">
+        <v>114</v>
+      </c>
+      <c r="H90">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>115</v>
+      </c>
+      <c r="B91" t="s">
+        <v>91</v>
+      </c>
+      <c r="C91" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" t="s">
+        <v>114</v>
+      </c>
+      <c r="G91" t="s">
+        <v>116</v>
+      </c>
+      <c r="H91">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>117</v>
+      </c>
+      <c r="B92" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92" t="s">
+        <v>26</v>
+      </c>
+      <c r="D92" t="s">
+        <v>27</v>
+      </c>
+      <c r="E92" t="s">
+        <v>3</v>
+      </c>
+      <c r="F92" t="s">
+        <v>119</v>
+      </c>
+      <c r="G92" t="s">
+        <v>120</v>
+      </c>
+      <c r="H92">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>121</v>
+      </c>
+      <c r="B93" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" t="s">
+        <v>31</v>
+      </c>
+      <c r="D93" t="s">
+        <v>27</v>
+      </c>
+      <c r="E93" t="s">
+        <v>3</v>
+      </c>
+      <c r="F93" t="s">
+        <v>120</v>
+      </c>
+      <c r="G93" t="s">
+        <v>122</v>
+      </c>
+      <c r="H93">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>123</v>
+      </c>
+      <c r="B94" t="s">
+        <v>118</v>
+      </c>
+      <c r="C94" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" t="s">
+        <v>27</v>
+      </c>
+      <c r="E94" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" t="s">
+        <v>124</v>
+      </c>
+      <c r="G94" t="s">
+        <v>125</v>
+      </c>
+      <c r="H94">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>126</v>
+      </c>
+      <c r="B95" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" t="s">
+        <v>38</v>
+      </c>
+      <c r="D95" t="s">
+        <v>27</v>
+      </c>
+      <c r="E95" t="s">
+        <v>3</v>
+      </c>
+      <c r="F95" t="s">
+        <v>127</v>
+      </c>
+      <c r="G95" t="s">
+        <v>128</v>
+      </c>
+      <c r="H95">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>129</v>
+      </c>
+      <c r="B96" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" t="s">
+        <v>41</v>
+      </c>
+      <c r="D96" t="s">
+        <v>27</v>
+      </c>
+      <c r="E96" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" t="s">
+        <v>128</v>
+      </c>
+      <c r="G96" t="s">
+        <v>130</v>
+      </c>
+      <c r="H96">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>131</v>
+      </c>
+      <c r="B97" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" t="s">
+        <v>45</v>
+      </c>
+      <c r="D97" t="s">
+        <v>27</v>
+      </c>
+      <c r="E97" t="s">
+        <v>3</v>
+      </c>
+      <c r="F97" t="s">
+        <v>130</v>
+      </c>
+      <c r="G97" t="s">
+        <v>132</v>
+      </c>
+      <c r="H97">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>133</v>
+      </c>
+      <c r="B98" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" t="s">
+        <v>49</v>
+      </c>
+      <c r="D98" t="s">
+        <v>27</v>
+      </c>
+      <c r="E98" t="s">
+        <v>3</v>
+      </c>
+      <c r="F98" t="s">
+        <v>132</v>
+      </c>
+      <c r="G98" t="s">
+        <v>134</v>
+      </c>
+      <c r="H98">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>135</v>
+      </c>
+      <c r="B99" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99" t="s">
+        <v>53</v>
+      </c>
+      <c r="D99" t="s">
+        <v>27</v>
+      </c>
+      <c r="E99" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G99" t="s">
         <v>137</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H99">
+        <v>45001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>138</v>
+      </c>
+      <c r="B100" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" t="s">
+        <v>27</v>
+      </c>
+      <c r="E100" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" t="s">
+        <v>137</v>
+      </c>
+      <c r="G100" t="s">
+        <v>139</v>
+      </c>
+      <c r="H100">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>140</v>
+      </c>
+      <c r="B101" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" t="s">
+        <v>27</v>
+      </c>
+      <c r="E101" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" t="s">
+        <v>141</v>
+      </c>
+      <c r="G101" t="s">
+        <v>142</v>
+      </c>
+      <c r="H101">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>24</v>
+      </c>
+      <c r="B102" t="s">
+        <v>25</v>
+      </c>
+      <c r="C102" t="s">
+        <v>26</v>
+      </c>
+      <c r="D102" t="s">
+        <v>27</v>
+      </c>
+      <c r="E102" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" t="s">
+        <v>29</v>
+      </c>
+      <c r="H102">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" t="s">
+        <v>31</v>
+      </c>
+      <c r="D103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103" t="s">
+        <v>3</v>
+      </c>
+      <c r="F103" t="s">
+        <v>29</v>
+      </c>
+      <c r="G103" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>25</v>
+      </c>
+      <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" t="s">
+        <v>35</v>
+      </c>
+      <c r="G104" t="s">
+        <v>36</v>
+      </c>
+      <c r="H104">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" t="s">
+        <v>38</v>
+      </c>
+      <c r="D105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105" t="s">
+        <v>3</v>
+      </c>
+      <c r="F105" t="s">
+        <v>36</v>
+      </c>
+      <c r="G105" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s">
+        <v>25</v>
+      </c>
+      <c r="C106" t="s">
+        <v>41</v>
+      </c>
+      <c r="D106" t="s">
+        <v>27</v>
+      </c>
+      <c r="E106" t="s">
+        <v>3</v>
+      </c>
+      <c r="F106" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" t="s">
+        <v>43</v>
+      </c>
+      <c r="H106">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" t="s">
+        <v>27</v>
+      </c>
+      <c r="E107" t="s">
+        <v>3</v>
+      </c>
+      <c r="F107" t="s">
+        <v>46</v>
+      </c>
+      <c r="G107" t="s">
+        <v>47</v>
+      </c>
+      <c r="H107">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>48</v>
+      </c>
+      <c r="B108" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" t="s">
+        <v>49</v>
+      </c>
+      <c r="D108" t="s">
+        <v>27</v>
+      </c>
+      <c r="E108" t="s">
+        <v>3</v>
+      </c>
+      <c r="F108" t="s">
+        <v>50</v>
+      </c>
+      <c r="G108" t="s">
+        <v>51</v>
+      </c>
+      <c r="H108">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" t="s">
+        <v>25</v>
+      </c>
+      <c r="C109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D109" t="s">
+        <v>27</v>
+      </c>
+      <c r="E109" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" t="s">
+        <v>54</v>
+      </c>
+      <c r="G109" t="s">
+        <v>55</v>
+      </c>
+      <c r="H109">
+        <v>45009</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>56</v>
+      </c>
+      <c r="B110" t="s">
+        <v>25</v>
+      </c>
+      <c r="C110" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110" t="s">
+        <v>27</v>
+      </c>
+      <c r="E110" t="s">
+        <v>3</v>
+      </c>
+      <c r="F110" t="s">
+        <v>55</v>
+      </c>
+      <c r="G110" t="s">
+        <v>58</v>
+      </c>
+      <c r="H110">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>59</v>
+      </c>
+      <c r="B111" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" t="s">
+        <v>60</v>
+      </c>
+      <c r="D111" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111" t="s">
+        <v>3</v>
+      </c>
+      <c r="F111" t="s">
+        <v>61</v>
+      </c>
+      <c r="G111" t="s">
+        <v>62</v>
+      </c>
+      <c r="H111">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>63</v>
+      </c>
+      <c r="B112" t="s">
+        <v>64</v>
+      </c>
+      <c r="C112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" t="s">
+        <v>27</v>
+      </c>
+      <c r="E112" t="s">
+        <v>3</v>
+      </c>
+      <c r="F112" t="s">
+        <v>65</v>
+      </c>
+      <c r="G112" t="s">
+        <v>66</v>
+      </c>
+      <c r="H112">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>67</v>
+      </c>
+      <c r="B113" t="s">
+        <v>64</v>
+      </c>
+      <c r="C113" t="s">
+        <v>31</v>
+      </c>
+      <c r="D113" t="s">
+        <v>27</v>
+      </c>
+      <c r="E113" t="s">
+        <v>3</v>
+      </c>
+      <c r="F113" t="s">
+        <v>68</v>
+      </c>
+      <c r="G113" t="s">
+        <v>69</v>
+      </c>
+      <c r="H113">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>70</v>
+      </c>
+      <c r="B114" t="s">
+        <v>64</v>
+      </c>
+      <c r="C114" t="s">
+        <v>34</v>
+      </c>
+      <c r="D114" t="s">
+        <v>27</v>
+      </c>
+      <c r="E114" t="s">
+        <v>3</v>
+      </c>
+      <c r="F114" t="s">
+        <v>69</v>
+      </c>
+      <c r="G114" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>72</v>
+      </c>
+      <c r="B115" t="s">
+        <v>64</v>
+      </c>
+      <c r="C115" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" t="s">
+        <v>27</v>
+      </c>
+      <c r="E115" t="s">
+        <v>3</v>
+      </c>
+      <c r="F115" t="s">
+        <v>73</v>
+      </c>
+      <c r="G115" t="s">
+        <v>74</v>
+      </c>
+      <c r="H115">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" t="s">
+        <v>64</v>
+      </c>
+      <c r="C116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D116" t="s">
+        <v>27</v>
+      </c>
+      <c r="E116" t="s">
+        <v>3</v>
+      </c>
+      <c r="F116" t="s">
+        <v>76</v>
+      </c>
+      <c r="G116" t="s">
+        <v>77</v>
+      </c>
+      <c r="H116">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>78</v>
+      </c>
+      <c r="B117" t="s">
+        <v>64</v>
+      </c>
+      <c r="C117" t="s">
+        <v>45</v>
+      </c>
+      <c r="D117" t="s">
+        <v>27</v>
+      </c>
+      <c r="E117" t="s">
+        <v>3</v>
+      </c>
+      <c r="F117" t="s">
+        <v>77</v>
+      </c>
+      <c r="G117" t="s">
+        <v>79</v>
+      </c>
+      <c r="H117">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>80</v>
+      </c>
+      <c r="B118" t="s">
+        <v>64</v>
+      </c>
+      <c r="C118" t="s">
+        <v>49</v>
+      </c>
+      <c r="D118" t="s">
+        <v>27</v>
+      </c>
+      <c r="E118" t="s">
+        <v>3</v>
+      </c>
+      <c r="F118" t="s">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s">
+        <v>81</v>
+      </c>
+      <c r="H118">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>82</v>
+      </c>
+      <c r="B119" t="s">
+        <v>64</v>
+      </c>
+      <c r="C119" t="s">
+        <v>53</v>
+      </c>
+      <c r="D119" t="s">
+        <v>27</v>
+      </c>
+      <c r="E119" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" t="s">
+        <v>83</v>
+      </c>
+      <c r="G119" t="s">
+        <v>84</v>
+      </c>
+      <c r="H119">
+        <v>45004</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>85</v>
+      </c>
+      <c r="B120" t="s">
+        <v>64</v>
+      </c>
+      <c r="C120" t="s">
+        <v>57</v>
+      </c>
+      <c r="D120" t="s">
+        <v>27</v>
+      </c>
+      <c r="E120" t="s">
+        <v>3</v>
+      </c>
+      <c r="F120" t="s">
+        <v>84</v>
+      </c>
+      <c r="G120" t="s">
+        <v>86</v>
+      </c>
+      <c r="H120">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>87</v>
+      </c>
+      <c r="B121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121" t="s">
+        <v>60</v>
+      </c>
+      <c r="D121" t="s">
+        <v>27</v>
+      </c>
+      <c r="E121" t="s">
+        <v>3</v>
+      </c>
+      <c r="F121" t="s">
+        <v>88</v>
+      </c>
+      <c r="G121" t="s">
+        <v>89</v>
+      </c>
+      <c r="H121">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>90</v>
+      </c>
+      <c r="B122" t="s">
+        <v>91</v>
+      </c>
+      <c r="C122" t="s">
+        <v>26</v>
+      </c>
+      <c r="D122" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122" t="s">
+        <v>3</v>
+      </c>
+      <c r="F122" t="s">
+        <v>92</v>
+      </c>
+      <c r="G122" t="s">
+        <v>93</v>
+      </c>
+      <c r="H122">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>94</v>
+      </c>
+      <c r="B123" t="s">
+        <v>91</v>
+      </c>
+      <c r="C123" t="s">
+        <v>31</v>
+      </c>
+      <c r="D123" t="s">
+        <v>27</v>
+      </c>
+      <c r="E123" t="s">
+        <v>3</v>
+      </c>
+      <c r="F123" t="s">
+        <v>93</v>
+      </c>
+      <c r="G123" t="s">
+        <v>95</v>
+      </c>
+      <c r="H123">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>96</v>
+      </c>
+      <c r="B124" t="s">
+        <v>91</v>
+      </c>
+      <c r="C124" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" t="s">
+        <v>27</v>
+      </c>
+      <c r="E124" t="s">
+        <v>3</v>
+      </c>
+      <c r="F124" t="s">
+        <v>97</v>
+      </c>
+      <c r="G124" t="s">
+        <v>98</v>
+      </c>
+      <c r="H124">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>99</v>
+      </c>
+      <c r="B125" t="s">
+        <v>91</v>
+      </c>
+      <c r="C125" t="s">
+        <v>38</v>
+      </c>
+      <c r="D125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E125" t="s">
+        <v>3</v>
+      </c>
+      <c r="F125" t="s">
+        <v>100</v>
+      </c>
+      <c r="G125" t="s">
+        <v>101</v>
+      </c>
+      <c r="H125">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>102</v>
+      </c>
+      <c r="B126" t="s">
+        <v>91</v>
+      </c>
+      <c r="C126" t="s">
+        <v>41</v>
+      </c>
+      <c r="D126" t="s">
+        <v>27</v>
+      </c>
+      <c r="E126" t="s">
+        <v>3</v>
+      </c>
+      <c r="F126" t="s">
+        <v>103</v>
+      </c>
+      <c r="G126" t="s">
+        <v>104</v>
+      </c>
+      <c r="H126">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" t="s">
+        <v>91</v>
+      </c>
+      <c r="C127" t="s">
+        <v>45</v>
+      </c>
+      <c r="D127" t="s">
+        <v>27</v>
+      </c>
+      <c r="E127" t="s">
+        <v>3</v>
+      </c>
+      <c r="F127" t="s">
+        <v>104</v>
+      </c>
+      <c r="G127" t="s">
+        <v>106</v>
+      </c>
+      <c r="H127">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>107</v>
+      </c>
+      <c r="B128" t="s">
+        <v>91</v>
+      </c>
+      <c r="C128" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" t="s">
+        <v>27</v>
+      </c>
+      <c r="E128" t="s">
+        <v>3</v>
+      </c>
+      <c r="F128" t="s">
+        <v>106</v>
+      </c>
+      <c r="G128" t="s">
+        <v>108</v>
+      </c>
+      <c r="H128">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>109</v>
+      </c>
+      <c r="B129" t="s">
+        <v>91</v>
+      </c>
+      <c r="C129" t="s">
+        <v>53</v>
+      </c>
+      <c r="D129" t="s">
+        <v>27</v>
+      </c>
+      <c r="E129" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" t="s">
+        <v>110</v>
+      </c>
+      <c r="G129" t="s">
+        <v>111</v>
+      </c>
+      <c r="H129">
+        <v>45013</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>112</v>
+      </c>
+      <c r="B130" t="s">
+        <v>91</v>
+      </c>
+      <c r="C130" t="s">
+        <v>57</v>
+      </c>
+      <c r="D130" t="s">
+        <v>27</v>
+      </c>
+      <c r="E130" t="s">
+        <v>3</v>
+      </c>
+      <c r="F130" t="s">
+        <v>113</v>
+      </c>
+      <c r="G130" t="s">
+        <v>114</v>
+      </c>
+      <c r="H130">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>115</v>
+      </c>
+      <c r="B131" t="s">
+        <v>91</v>
+      </c>
+      <c r="C131" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" t="s">
+        <v>27</v>
+      </c>
+      <c r="E131" t="s">
+        <v>3</v>
+      </c>
+      <c r="F131" t="s">
+        <v>114</v>
+      </c>
+      <c r="G131" t="s">
+        <v>116</v>
+      </c>
+      <c r="H131">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>117</v>
+      </c>
+      <c r="B132" t="s">
+        <v>118</v>
+      </c>
+      <c r="C132" t="s">
+        <v>26</v>
+      </c>
+      <c r="D132" t="s">
+        <v>27</v>
+      </c>
+      <c r="E132" t="s">
+        <v>3</v>
+      </c>
+      <c r="F132" t="s">
+        <v>119</v>
+      </c>
+      <c r="G132" t="s">
+        <v>120</v>
+      </c>
+      <c r="H132">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>121</v>
+      </c>
+      <c r="B133" t="s">
+        <v>118</v>
+      </c>
+      <c r="C133" t="s">
+        <v>31</v>
+      </c>
+      <c r="D133" t="s">
+        <v>27</v>
+      </c>
+      <c r="E133" t="s">
+        <v>3</v>
+      </c>
+      <c r="F133" t="s">
+        <v>120</v>
+      </c>
+      <c r="G133" t="s">
+        <v>122</v>
+      </c>
+      <c r="H133">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>123</v>
+      </c>
+      <c r="B134" t="s">
+        <v>118</v>
+      </c>
+      <c r="C134" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" t="s">
+        <v>27</v>
+      </c>
+      <c r="E134" t="s">
+        <v>3</v>
+      </c>
+      <c r="F134" t="s">
+        <v>124</v>
+      </c>
+      <c r="G134" t="s">
+        <v>125</v>
+      </c>
+      <c r="H134">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>126</v>
+      </c>
+      <c r="B135" t="s">
+        <v>118</v>
+      </c>
+      <c r="C135" t="s">
+        <v>38</v>
+      </c>
+      <c r="D135" t="s">
+        <v>27</v>
+      </c>
+      <c r="E135" t="s">
+        <v>3</v>
+      </c>
+      <c r="F135" t="s">
+        <v>127</v>
+      </c>
+      <c r="G135" t="s">
+        <v>128</v>
+      </c>
+      <c r="H135">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>129</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B136" t="s">
+        <v>118</v>
+      </c>
+      <c r="C136" t="s">
+        <v>41</v>
+      </c>
+      <c r="D136" t="s">
+        <v>27</v>
+      </c>
+      <c r="E136" t="s">
+        <v>3</v>
+      </c>
+      <c r="F136" t="s">
+        <v>128</v>
+      </c>
+      <c r="G136" t="s">
+        <v>130</v>
+      </c>
+      <c r="H136">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>131</v>
+      </c>
+      <c r="B137" t="s">
+        <v>118</v>
+      </c>
+      <c r="C137" t="s">
+        <v>45</v>
+      </c>
+      <c r="D137" t="s">
+        <v>27</v>
+      </c>
+      <c r="E137" t="s">
+        <v>3</v>
+      </c>
+      <c r="F137" t="s">
+        <v>130</v>
+      </c>
+      <c r="G137" t="s">
+        <v>132</v>
+      </c>
+      <c r="H137">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>133</v>
+      </c>
+      <c r="B138" t="s">
+        <v>118</v>
+      </c>
+      <c r="C138" t="s">
+        <v>49</v>
+      </c>
+      <c r="D138" t="s">
+        <v>27</v>
+      </c>
+      <c r="E138" t="s">
+        <v>3</v>
+      </c>
+      <c r="F138" t="s">
+        <v>132</v>
+      </c>
+      <c r="G138" t="s">
+        <v>134</v>
+      </c>
+      <c r="H138">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>135</v>
+      </c>
+      <c r="B139" t="s">
+        <v>118</v>
+      </c>
+      <c r="C139" t="s">
+        <v>53</v>
+      </c>
+      <c r="D139" t="s">
+        <v>27</v>
+      </c>
+      <c r="E139" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" t="s">
+        <v>136</v>
+      </c>
+      <c r="G139" t="s">
+        <v>137</v>
+      </c>
+      <c r="H139">
+        <v>45001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
         <v>138</v>
       </c>
-      <c r="D31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" t="s">
-        <v>3</v>
-      </c>
-      <c r="F31" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="B140" t="s">
+        <v>118</v>
+      </c>
+      <c r="C140" t="s">
+        <v>57</v>
+      </c>
+      <c r="D140" t="s">
+        <v>27</v>
+      </c>
+      <c r="E140" t="s">
+        <v>3</v>
+      </c>
+      <c r="F140" t="s">
+        <v>137</v>
+      </c>
+      <c r="G140" t="s">
         <v>139</v>
       </c>
-      <c r="H31">
-        <v>62</v>
+      <c r="H140">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>118</v>
+      </c>
+      <c r="C141" t="s">
+        <v>60</v>
+      </c>
+      <c r="D141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E141" t="s">
+        <v>3</v>
+      </c>
+      <c r="F141" t="s">
+        <v>141</v>
+      </c>
+      <c r="G141" t="s">
+        <v>142</v>
+      </c>
+      <c r="H141">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" t="s">
+        <v>144</v>
+      </c>
+      <c r="C142" t="s">
+        <v>26</v>
+      </c>
+      <c r="D142" t="s">
+        <v>27</v>
+      </c>
+      <c r="E142" t="s">
+        <v>3</v>
+      </c>
+      <c r="F142" t="s">
+        <v>145</v>
+      </c>
+      <c r="G142" t="s">
+        <v>146</v>
+      </c>
+      <c r="H142">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>147</v>
+      </c>
+      <c r="B143" t="s">
+        <v>144</v>
+      </c>
+      <c r="C143" t="s">
+        <v>31</v>
+      </c>
+      <c r="D143" t="s">
+        <v>27</v>
+      </c>
+      <c r="E143" t="s">
+        <v>3</v>
+      </c>
+      <c r="F143" t="s">
+        <v>146</v>
+      </c>
+      <c r="G143" t="s">
+        <v>148</v>
+      </c>
+      <c r="H143">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" t="s">
+        <v>144</v>
+      </c>
+      <c r="C144" t="s">
+        <v>34</v>
+      </c>
+      <c r="D144" t="s">
+        <v>27</v>
+      </c>
+      <c r="E144" t="s">
+        <v>3</v>
+      </c>
+      <c r="F144" t="s">
+        <v>150</v>
+      </c>
+      <c r="G144" t="s">
+        <v>151</v>
+      </c>
+      <c r="H144">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" t="s">
+        <v>144</v>
+      </c>
+      <c r="C145" t="s">
+        <v>38</v>
+      </c>
+      <c r="D145" t="s">
+        <v>27</v>
+      </c>
+      <c r="E145" t="s">
+        <v>3</v>
+      </c>
+      <c r="F145" t="s">
+        <v>151</v>
+      </c>
+      <c r="G145" t="s">
+        <v>153</v>
+      </c>
+      <c r="H145">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146" t="s">
+        <v>144</v>
+      </c>
+      <c r="C146" t="s">
+        <v>41</v>
+      </c>
+      <c r="D146" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146" t="s">
+        <v>3</v>
+      </c>
+      <c r="F146" t="s">
+        <v>153</v>
+      </c>
+      <c r="G146" t="s">
+        <v>155</v>
+      </c>
+      <c r="H146">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" t="s">
+        <v>144</v>
+      </c>
+      <c r="C147" t="s">
+        <v>45</v>
+      </c>
+      <c r="D147" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" t="s">
+        <v>3</v>
+      </c>
+      <c r="F147" t="s">
+        <v>155</v>
+      </c>
+      <c r="G147" t="s">
+        <v>157</v>
+      </c>
+      <c r="H147">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>158</v>
+      </c>
+      <c r="B148" t="s">
+        <v>144</v>
+      </c>
+      <c r="C148" t="s">
+        <v>49</v>
+      </c>
+      <c r="D148" t="s">
+        <v>27</v>
+      </c>
+      <c r="E148" t="s">
+        <v>3</v>
+      </c>
+      <c r="F148" t="s">
+        <v>157</v>
+      </c>
+      <c r="G148" t="s">
+        <v>159</v>
+      </c>
+      <c r="H148">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>160</v>
+      </c>
+      <c r="B149" t="s">
+        <v>144</v>
+      </c>
+      <c r="C149" t="s">
+        <v>53</v>
+      </c>
+      <c r="D149" t="s">
+        <v>27</v>
+      </c>
+      <c r="E149" t="s">
+        <v>4</v>
+      </c>
+      <c r="F149" t="s">
+        <v>161</v>
+      </c>
+      <c r="G149" t="s">
+        <v>162</v>
+      </c>
+      <c r="H149">
+        <v>45016</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>163</v>
+      </c>
+      <c r="B150" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150" t="s">
+        <v>27</v>
+      </c>
+      <c r="E150" t="s">
+        <v>3</v>
+      </c>
+      <c r="F150" t="s">
+        <v>164</v>
+      </c>
+      <c r="G150" t="s">
+        <v>165</v>
+      </c>
+      <c r="H150">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>166</v>
+      </c>
+      <c r="B151" t="s">
+        <v>144</v>
+      </c>
+      <c r="C151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D151" t="s">
+        <v>27</v>
+      </c>
+      <c r="E151" t="s">
+        <v>3</v>
+      </c>
+      <c r="F151" t="s">
+        <v>165</v>
+      </c>
+      <c r="G151" t="s">
+        <v>167</v>
+      </c>
+      <c r="H151">
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -1749,7 +5105,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1761,19 +5117,274 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" t="s">
+        <v>179</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1784,7 +5395,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1796,529 +5407,2569 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E12" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E14" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D18" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E18" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E20" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E21" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E23" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E24" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E27" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E28" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>195</v>
       </c>
       <c r="E29" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" t="s">
+        <v>192</v>
+      </c>
+      <c r="E32" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>191</v>
+      </c>
+      <c r="D33" t="s">
+        <v>192</v>
+      </c>
+      <c r="E33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D34" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>191</v>
+      </c>
+      <c r="D36" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>192</v>
+      </c>
+      <c r="E37" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D40" t="s">
+        <v>192</v>
+      </c>
+      <c r="E40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D41" t="s">
+        <v>192</v>
+      </c>
+      <c r="E41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>191</v>
+      </c>
+      <c r="D42" t="s">
+        <v>192</v>
+      </c>
+      <c r="E42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" t="s">
+        <v>191</v>
+      </c>
+      <c r="D43" t="s">
+        <v>192</v>
+      </c>
+      <c r="E43" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s">
+        <v>191</v>
+      </c>
+      <c r="D45" t="s">
+        <v>192</v>
+      </c>
+      <c r="E45" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E46" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" t="s">
+        <v>192</v>
+      </c>
+      <c r="E48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" t="s">
+        <v>192</v>
+      </c>
+      <c r="E50" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>191</v>
+      </c>
+      <c r="D52" t="s">
+        <v>192</v>
+      </c>
+      <c r="E52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D53" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" t="s">
+        <v>191</v>
+      </c>
+      <c r="D54" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" t="s">
+        <v>192</v>
+      </c>
+      <c r="E55" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" t="s">
+        <v>192</v>
+      </c>
+      <c r="E56" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>106</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57" t="s">
+        <v>192</v>
+      </c>
+      <c r="E57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" t="s">
+        <v>191</v>
+      </c>
+      <c r="D58" t="s">
+        <v>192</v>
+      </c>
+      <c r="E58" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" t="s">
+        <v>194</v>
+      </c>
+      <c r="D59" t="s">
+        <v>195</v>
+      </c>
+      <c r="E59" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" t="s">
+        <v>191</v>
+      </c>
+      <c r="D61" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>191</v>
+      </c>
+      <c r="D62" t="s">
+        <v>192</v>
+      </c>
+      <c r="E62" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" t="s">
+        <v>191</v>
+      </c>
+      <c r="D63" t="s">
+        <v>192</v>
+      </c>
+      <c r="E63" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" t="s">
+        <v>192</v>
+      </c>
+      <c r="E65" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" t="s">
+        <v>191</v>
+      </c>
+      <c r="D67" t="s">
+        <v>192</v>
+      </c>
+      <c r="E67" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>51</v>
+      </c>
+      <c r="B68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" t="s">
+        <v>192</v>
+      </c>
+      <c r="E68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" t="s">
+        <v>194</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" t="s">
+        <v>60</v>
+      </c>
+      <c r="C71" t="s">
+        <v>191</v>
+      </c>
+      <c r="D71" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>191</v>
+      </c>
+      <c r="D72" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" t="s">
+        <v>192</v>
+      </c>
+      <c r="E74" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C75" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" t="s">
+        <v>192</v>
+      </c>
+      <c r="E75" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>77</v>
+      </c>
+      <c r="B76" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" t="s">
+        <v>191</v>
+      </c>
+      <c r="D77" t="s">
+        <v>192</v>
+      </c>
+      <c r="E77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" t="s">
+        <v>191</v>
+      </c>
+      <c r="D78" t="s">
+        <v>192</v>
+      </c>
+      <c r="E78" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" t="s">
+        <v>194</v>
+      </c>
+      <c r="D79" t="s">
+        <v>195</v>
+      </c>
+      <c r="E79" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" t="s">
+        <v>191</v>
+      </c>
+      <c r="D80" t="s">
+        <v>192</v>
+      </c>
+      <c r="E80" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" t="s">
+        <v>60</v>
+      </c>
+      <c r="C81" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>191</v>
+      </c>
+      <c r="D82" t="s">
+        <v>192</v>
+      </c>
+      <c r="E82" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>191</v>
+      </c>
+      <c r="D83" t="s">
+        <v>192</v>
+      </c>
+      <c r="E83" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" t="s">
+        <v>192</v>
+      </c>
+      <c r="E84" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" t="s">
+        <v>38</v>
+      </c>
+      <c r="C85" t="s">
+        <v>191</v>
+      </c>
+      <c r="D85" t="s">
+        <v>192</v>
+      </c>
+      <c r="E85" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>104</v>
+      </c>
+      <c r="B86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s">
+        <v>191</v>
+      </c>
+      <c r="D86" t="s">
+        <v>192</v>
+      </c>
+      <c r="E86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" t="s">
+        <v>191</v>
+      </c>
+      <c r="D87" t="s">
+        <v>192</v>
+      </c>
+      <c r="E87" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" t="s">
+        <v>49</v>
+      </c>
+      <c r="C88" t="s">
+        <v>191</v>
+      </c>
+      <c r="D88" t="s">
+        <v>192</v>
+      </c>
+      <c r="E88" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>111</v>
+      </c>
+      <c r="B89" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89" t="s">
+        <v>194</v>
+      </c>
+      <c r="D89" t="s">
+        <v>195</v>
+      </c>
+      <c r="E89" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>114</v>
+      </c>
+      <c r="B90" t="s">
+        <v>57</v>
+      </c>
+      <c r="C90" t="s">
+        <v>191</v>
+      </c>
+      <c r="D90" t="s">
+        <v>192</v>
+      </c>
+      <c r="E90" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" t="s">
+        <v>60</v>
+      </c>
+      <c r="C91" t="s">
+        <v>191</v>
+      </c>
+      <c r="D91" t="s">
+        <v>192</v>
+      </c>
+      <c r="E91" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>120</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>191</v>
+      </c>
+      <c r="D92" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" t="s">
+        <v>191</v>
+      </c>
+      <c r="D93" t="s">
+        <v>192</v>
+      </c>
+      <c r="E93" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" t="s">
+        <v>191</v>
+      </c>
+      <c r="D94" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>128</v>
+      </c>
+      <c r="B95" t="s">
+        <v>38</v>
+      </c>
+      <c r="C95" t="s">
+        <v>191</v>
+      </c>
+      <c r="D95" t="s">
+        <v>192</v>
+      </c>
+      <c r="E95" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" t="s">
+        <v>41</v>
+      </c>
+      <c r="C96" t="s">
+        <v>191</v>
+      </c>
+      <c r="D96" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>132</v>
+      </c>
+      <c r="B97" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" t="s">
+        <v>191</v>
+      </c>
+      <c r="D97" t="s">
+        <v>192</v>
+      </c>
+      <c r="E97" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" t="s">
+        <v>49</v>
+      </c>
+      <c r="C98" t="s">
+        <v>191</v>
+      </c>
+      <c r="D98" t="s">
+        <v>192</v>
+      </c>
+      <c r="E98" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99" t="s">
+        <v>194</v>
+      </c>
+      <c r="D99" t="s">
+        <v>195</v>
+      </c>
+      <c r="E99" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>139</v>
       </c>
-      <c r="B31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" t="s">
-        <v>149</v>
-      </c>
-      <c r="D31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="B100" t="s">
+        <v>57</v>
+      </c>
+      <c r="C100" t="s">
+        <v>191</v>
+      </c>
+      <c r="D100" t="s">
+        <v>192</v>
+      </c>
+      <c r="E100" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>142</v>
+      </c>
+      <c r="B101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" t="s">
+        <v>191</v>
+      </c>
+      <c r="D101" t="s">
+        <v>192</v>
+      </c>
+      <c r="E101" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>190</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>191</v>
+      </c>
+      <c r="D102" t="s">
+        <v>192</v>
+      </c>
+      <c r="E102" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" t="s">
+        <v>31</v>
+      </c>
+      <c r="C103" t="s">
+        <v>191</v>
+      </c>
+      <c r="D103" t="s">
+        <v>192</v>
+      </c>
+      <c r="E103" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>36</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" t="s">
+        <v>191</v>
+      </c>
+      <c r="D104" t="s">
+        <v>192</v>
+      </c>
+      <c r="E104" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105" t="s">
+        <v>191</v>
+      </c>
+      <c r="D105" t="s">
+        <v>192</v>
+      </c>
+      <c r="E105" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" t="s">
+        <v>41</v>
+      </c>
+      <c r="C106" t="s">
+        <v>191</v>
+      </c>
+      <c r="D106" t="s">
+        <v>192</v>
+      </c>
+      <c r="E106" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>47</v>
+      </c>
+      <c r="B107" t="s">
+        <v>45</v>
+      </c>
+      <c r="C107" t="s">
+        <v>191</v>
+      </c>
+      <c r="D107" t="s">
+        <v>192</v>
+      </c>
+      <c r="E107" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>51</v>
+      </c>
+      <c r="B108" t="s">
+        <v>49</v>
+      </c>
+      <c r="C108" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" t="s">
+        <v>192</v>
+      </c>
+      <c r="E108" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>55</v>
+      </c>
+      <c r="B109" t="s">
+        <v>53</v>
+      </c>
+      <c r="C109" t="s">
+        <v>194</v>
+      </c>
+      <c r="D109" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>58</v>
+      </c>
+      <c r="B110" t="s">
+        <v>57</v>
+      </c>
+      <c r="C110" t="s">
+        <v>191</v>
+      </c>
+      <c r="D110" t="s">
+        <v>192</v>
+      </c>
+      <c r="E110" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" t="s">
+        <v>60</v>
+      </c>
+      <c r="C111" t="s">
+        <v>191</v>
+      </c>
+      <c r="D111" t="s">
+        <v>192</v>
+      </c>
+      <c r="E111" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>66</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>191</v>
+      </c>
+      <c r="D112" t="s">
+        <v>192</v>
+      </c>
+      <c r="E112" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>69</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" t="s">
+        <v>191</v>
+      </c>
+      <c r="D113" t="s">
+        <v>192</v>
+      </c>
+      <c r="E113" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>71</v>
+      </c>
+      <c r="B114" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" t="s">
+        <v>191</v>
+      </c>
+      <c r="D114" t="s">
+        <v>192</v>
+      </c>
+      <c r="E114" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>74</v>
+      </c>
+      <c r="B115" t="s">
+        <v>38</v>
+      </c>
+      <c r="C115" t="s">
+        <v>191</v>
+      </c>
+      <c r="D115" t="s">
+        <v>192</v>
+      </c>
+      <c r="E115" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>77</v>
+      </c>
+      <c r="B116" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" t="s">
+        <v>191</v>
+      </c>
+      <c r="D116" t="s">
+        <v>192</v>
+      </c>
+      <c r="E116" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>79</v>
+      </c>
+      <c r="B117" t="s">
+        <v>45</v>
+      </c>
+      <c r="C117" t="s">
+        <v>191</v>
+      </c>
+      <c r="D117" t="s">
+        <v>192</v>
+      </c>
+      <c r="E117" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>81</v>
+      </c>
+      <c r="B118" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" t="s">
+        <v>191</v>
+      </c>
+      <c r="D118" t="s">
+        <v>192</v>
+      </c>
+      <c r="E118" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>84</v>
+      </c>
+      <c r="B119" t="s">
+        <v>53</v>
+      </c>
+      <c r="C119" t="s">
+        <v>194</v>
+      </c>
+      <c r="D119" t="s">
+        <v>195</v>
+      </c>
+      <c r="E119" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>86</v>
+      </c>
+      <c r="B120" t="s">
+        <v>57</v>
+      </c>
+      <c r="C120" t="s">
+        <v>191</v>
+      </c>
+      <c r="D120" t="s">
+        <v>192</v>
+      </c>
+      <c r="E120" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>89</v>
+      </c>
+      <c r="B121" t="s">
+        <v>60</v>
+      </c>
+      <c r="C121" t="s">
+        <v>191</v>
+      </c>
+      <c r="D121" t="s">
+        <v>192</v>
+      </c>
+      <c r="E121" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>93</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>191</v>
+      </c>
+      <c r="D122" t="s">
+        <v>192</v>
+      </c>
+      <c r="E122" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>95</v>
+      </c>
+      <c r="B123" t="s">
+        <v>31</v>
+      </c>
+      <c r="C123" t="s">
+        <v>191</v>
+      </c>
+      <c r="D123" t="s">
+        <v>192</v>
+      </c>
+      <c r="E123" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>98</v>
+      </c>
+      <c r="B124" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" t="s">
+        <v>191</v>
+      </c>
+      <c r="D124" t="s">
+        <v>192</v>
+      </c>
+      <c r="E124" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+      <c r="B125" t="s">
+        <v>38</v>
+      </c>
+      <c r="C125" t="s">
+        <v>191</v>
+      </c>
+      <c r="D125" t="s">
+        <v>192</v>
+      </c>
+      <c r="E125" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" t="s">
+        <v>191</v>
+      </c>
+      <c r="D126" t="s">
+        <v>192</v>
+      </c>
+      <c r="E126" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>106</v>
+      </c>
+      <c r="B127" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127" t="s">
+        <v>191</v>
+      </c>
+      <c r="D127" t="s">
+        <v>192</v>
+      </c>
+      <c r="E127" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>108</v>
+      </c>
+      <c r="B128" t="s">
+        <v>49</v>
+      </c>
+      <c r="C128" t="s">
+        <v>191</v>
+      </c>
+      <c r="D128" t="s">
+        <v>192</v>
+      </c>
+      <c r="E128" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B129" t="s">
+        <v>53</v>
+      </c>
+      <c r="C129" t="s">
+        <v>194</v>
+      </c>
+      <c r="D129" t="s">
+        <v>195</v>
+      </c>
+      <c r="E129" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>114</v>
+      </c>
+      <c r="B130" t="s">
+        <v>57</v>
+      </c>
+      <c r="C130" t="s">
+        <v>191</v>
+      </c>
+      <c r="D130" t="s">
+        <v>192</v>
+      </c>
+      <c r="E130" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>116</v>
+      </c>
+      <c r="B131" t="s">
+        <v>60</v>
+      </c>
+      <c r="C131" t="s">
+        <v>191</v>
+      </c>
+      <c r="D131" t="s">
+        <v>192</v>
+      </c>
+      <c r="E131" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>120</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>191</v>
+      </c>
+      <c r="D132" t="s">
+        <v>192</v>
+      </c>
+      <c r="E132" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>122</v>
+      </c>
+      <c r="B133" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" t="s">
+        <v>191</v>
+      </c>
+      <c r="D133" t="s">
+        <v>192</v>
+      </c>
+      <c r="E133" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>125</v>
+      </c>
+      <c r="B134" t="s">
+        <v>34</v>
+      </c>
+      <c r="C134" t="s">
+        <v>191</v>
+      </c>
+      <c r="D134" t="s">
+        <v>192</v>
+      </c>
+      <c r="E134" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>128</v>
+      </c>
+      <c r="B135" t="s">
+        <v>38</v>
+      </c>
+      <c r="C135" t="s">
+        <v>191</v>
+      </c>
+      <c r="D135" t="s">
+        <v>192</v>
+      </c>
+      <c r="E135" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>130</v>
+      </c>
+      <c r="B136" t="s">
+        <v>41</v>
+      </c>
+      <c r="C136" t="s">
+        <v>191</v>
+      </c>
+      <c r="D136" t="s">
+        <v>192</v>
+      </c>
+      <c r="E136" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>132</v>
+      </c>
+      <c r="B137" t="s">
+        <v>45</v>
+      </c>
+      <c r="C137" t="s">
+        <v>191</v>
+      </c>
+      <c r="D137" t="s">
+        <v>192</v>
+      </c>
+      <c r="E137" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>49</v>
+      </c>
+      <c r="C138" t="s">
+        <v>191</v>
+      </c>
+      <c r="D138" t="s">
+        <v>192</v>
+      </c>
+      <c r="E138" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>137</v>
+      </c>
+      <c r="B139" t="s">
+        <v>53</v>
+      </c>
+      <c r="C139" t="s">
+        <v>194</v>
+      </c>
+      <c r="D139" t="s">
+        <v>195</v>
+      </c>
+      <c r="E139" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>57</v>
+      </c>
+      <c r="C140" t="s">
+        <v>191</v>
+      </c>
+      <c r="D140" t="s">
+        <v>192</v>
+      </c>
+      <c r="E140" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" t="s">
+        <v>60</v>
+      </c>
+      <c r="C141" t="s">
+        <v>191</v>
+      </c>
+      <c r="D141" t="s">
+        <v>192</v>
+      </c>
+      <c r="E141" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>191</v>
+      </c>
+      <c r="D142" t="s">
+        <v>192</v>
+      </c>
+      <c r="E142" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>148</v>
+      </c>
+      <c r="B143" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" t="s">
+        <v>191</v>
+      </c>
+      <c r="D143" t="s">
+        <v>192</v>
+      </c>
+      <c r="E143" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>151</v>
+      </c>
+      <c r="B144" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144" t="s">
+        <v>191</v>
+      </c>
+      <c r="D144" t="s">
+        <v>192</v>
+      </c>
+      <c r="E144" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145" t="s">
+        <v>38</v>
+      </c>
+      <c r="C145" t="s">
+        <v>191</v>
+      </c>
+      <c r="D145" t="s">
+        <v>192</v>
+      </c>
+      <c r="E145" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" t="s">
+        <v>191</v>
+      </c>
+      <c r="D146" t="s">
+        <v>192</v>
+      </c>
+      <c r="E146" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>157</v>
+      </c>
+      <c r="B147" t="s">
+        <v>45</v>
+      </c>
+      <c r="C147" t="s">
+        <v>191</v>
+      </c>
+      <c r="D147" t="s">
+        <v>192</v>
+      </c>
+      <c r="E147" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>159</v>
+      </c>
+      <c r="B148" t="s">
+        <v>49</v>
+      </c>
+      <c r="C148" t="s">
+        <v>191</v>
+      </c>
+      <c r="D148" t="s">
+        <v>192</v>
+      </c>
+      <c r="E148" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>162</v>
+      </c>
+      <c r="B149" t="s">
+        <v>53</v>
+      </c>
+      <c r="C149" t="s">
+        <v>194</v>
+      </c>
+      <c r="D149" t="s">
+        <v>195</v>
+      </c>
+      <c r="E149" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>165</v>
+      </c>
+      <c r="B150" t="s">
+        <v>57</v>
+      </c>
+      <c r="C150" t="s">
+        <v>191</v>
+      </c>
+      <c r="D150" t="s">
+        <v>192</v>
+      </c>
+      <c r="E150" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>167</v>
+      </c>
+      <c r="B151" t="s">
+        <v>60</v>
+      </c>
+      <c r="C151" t="s">
+        <v>191</v>
+      </c>
+      <c r="D151" t="s">
+        <v>192</v>
+      </c>
+      <c r="E151" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
